--- a/projects/project-3/assignment/src/data/ccot-axioms.xlsx
+++ b/projects/project-3/assignment/src/data/ccot-axioms.xlsx
@@ -565,7 +565,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf nb9c1f3fc66684fad90c47e8684c6d574b9</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n5bbd0065835348f99f10311c2165f2dcb9</t>
         </is>
       </c>
     </row>
@@ -667,7 +667,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf nb9c1f3fc66684fad90c47e8684c6d574b13</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n5bbd0065835348f99f10311c2165f2dcb13</t>
         </is>
       </c>
     </row>
@@ -701,7 +701,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf nb9c1f3fc66684fad90c47e8684c6d574b7</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n5bbd0065835348f99f10311c2165f2dcb7</t>
         </is>
       </c>
     </row>
@@ -769,7 +769,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf nb9c1f3fc66684fad90c47e8684c6d574b2</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n5bbd0065835348f99f10311c2165f2dcb2</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf nb9c1f3fc66684fad90c47e8684c6d574b5</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n5bbd0065835348f99f10311c2165f2dcb5</t>
         </is>
       </c>
     </row>
@@ -871,7 +871,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf nb9c1f3fc66684fad90c47e8684c6d574b3</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n5bbd0065835348f99f10311c2165f2dcb3</t>
         </is>
       </c>
     </row>
@@ -905,7 +905,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf nb9c1f3fc66684fad90c47e8684c6d574b1</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n5bbd0065835348f99f10311c2165f2dcb1</t>
         </is>
       </c>
     </row>
@@ -939,7 +939,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf nb9c1f3fc66684fad90c47e8684c6d574b15</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n5bbd0065835348f99f10311c2165f2dcb15</t>
         </is>
       </c>
     </row>
@@ -973,7 +973,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf nb9c1f3fc66684fad90c47e8684c6d574b6</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n5bbd0065835348f99f10311c2165f2dcb6</t>
         </is>
       </c>
     </row>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf nb9c1f3fc66684fad90c47e8684c6d574b14</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n5bbd0065835348f99f10311c2165f2dcb14</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf nb9c1f3fc66684fad90c47e8684c6d574b10</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n5bbd0065835348f99f10311c2165f2dcb10</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf nb9c1f3fc66684fad90c47e8684c6d574b16</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n5bbd0065835348f99f10311c2165f2dcb16</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf nb9c1f3fc66684fad90c47e8684c6d574b12</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n5bbd0065835348f99f10311c2165f2dcb12</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf nb9c1f3fc66684fad90c47e8684c6d574b4</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n5bbd0065835348f99f10311c2165f2dcb4</t>
         </is>
       </c>
     </row>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf nb9c1f3fc66684fad90c47e8684c6d574b8</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n5bbd0065835348f99f10311c2165f2dcb8</t>
         </is>
       </c>
     </row>
@@ -1262,7 +1262,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf nb9c1f3fc66684fad90c47e8684c6d574b11</t>
+          <t>http://www.w3.org/2000/01/rdf-schema#subClassOf n5bbd0065835348f99f10311c2165f2dcb11</t>
         </is>
       </c>
     </row>
